--- a/static/posh/VendorDataTemplate.xlsx
+++ b/static/posh/VendorDataTemplate.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>AB BBQ THANE RMALL</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr"/>
@@ -597,206 +597,167 @@
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="6" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Navi   Bhubhaneshwar</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>AB BBQ THANE KORUM MALL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SR.NO</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>VENDOR NAME</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>VENDOR'S MYPOSH UID</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>VENDOR'S COMMUNICATION ADDRESS*</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>MOBILE NUMBER*</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>EMAIL ID*</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>NATURE OF SERVICE</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>CONTACT PERSON NAME*</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>CONTACT PERSON MOBILE NO*</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>CONTACT PERSON EMAIL ID*</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>CONTRACT COMMENCEMENT DATE</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>CONTRACT EXPIRY DATE</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>MAX NUMBER OF EMPLOYEES DEPLOYED</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="9">
+      <c r="A9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="6" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>LOCATION</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>dawda adad</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="A10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SR.NO</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>VENDOR NAME</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>VENDOR'S MYPOSH UID</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>VENDOR'S COMMUNICATION ADDRESS*</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>MOBILE NUMBER*</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>EMAIL ID*</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>NATURE OF SERVICE</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>CONTACT PERSON NAME*</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>CONTACT PERSON MOBILE NO*</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>CONTACT PERSON EMAIL ID*</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACT COMMENCEMENT DATE</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACT EXPIRY DATE</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>MAX NUMBER OF EMPLOYEES DEPLOYED</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
@@ -811,22 +772,338 @@
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="6" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>AB BBQ KURLA R CITY MALL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SR.NO</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR NAME</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR'S MYPOSH UID</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR'S COMMUNICATION ADDRESS*</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>MOBILE NUMBER*</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL ID*</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>NATURE OF SERVICE</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON NAME*</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON MOBILE NO*</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON EMAIL ID*</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACT COMMENCEMENT DATE</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACT EXPIRY DATE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>MAX NUMBER OF EMPLOYEES DEPLOYED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="6" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>AB BBQ POWAI</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SR.NO</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR NAME</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR'S MYPOSH UID</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR'S COMMUNICATION ADDRESS*</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>MOBILE NUMBER*</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL ID*</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>NATURE OF SERVICE</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON NAME*</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON MOBILE NO*</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>CONTACT PERSON EMAIL ID*</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACT COMMENCEMENT DATE</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACT EXPIRY DATE</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>MAX NUMBER OF EMPLOYEES DEPLOYED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
